--- a/PCEComponentsLevel.xlsx
+++ b/PCEComponentsLevel.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF54BA45-C00B-45FA-B8BD-613AE12D7E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76ECC450-AD4E-4FA4-B360-2BF541302412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5F87E8F6-5A9D-48A4-8605-1C74292FD2A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Level" sheetId="23" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Level!$A$1:$D$1</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="1097">
   <si>
     <t>LineNumber</t>
   </si>
@@ -3123,15 +3126,6 @@
     <t>DNPIRA</t>
   </si>
   <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Gross output of nonprofit institutions (133)</t>
-  </si>
-  <si>
-    <t>DNPERA</t>
-  </si>
-  <si>
     <t>344</t>
   </si>
   <si>
@@ -3240,15 +3234,6 @@
     <t>DSNGRA</t>
   </si>
   <si>
-    <t>356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Less: Receipts from sales of goods and services by nonprofit institutions (134)</t>
-  </si>
-  <si>
-    <t>DNPSRA</t>
-  </si>
-  <si>
     <t>357</t>
   </si>
   <si>
@@ -3343,309 +3328,6 @@
   </si>
   <si>
     <t>DSNRRA</t>
-  </si>
-  <si>
-    <t>Additional aggregates:</t>
-  </si>
-  <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Control group</t>
-  </si>
-  <si>
-    <t>DCGPRA</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PCE food and energy</t>
-  </si>
-  <si>
-    <t>DPFERA</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PCE energy goods and services\1\</t>
-  </si>
-  <si>
-    <t>DNRGRA</t>
-  </si>
-  <si>
-    <t>372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PCE excluding food</t>
-  </si>
-  <si>
-    <t>DPXFRA</t>
-  </si>
-  <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PCE excluding energy</t>
-  </si>
-  <si>
-    <t>DPXERA</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PCE excluding food and energy\2\</t>
-  </si>
-  <si>
-    <t>DPCCRA</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PCE goods excluding food and energy\2\</t>
-  </si>
-  <si>
-    <t>IB000062</t>
-  </si>
-  <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PCE services excluding energy</t>
-  </si>
-  <si>
-    <t>IB000063</t>
-  </si>
-  <si>
-    <t>Market-based personal consumption expenditures (PCE):</t>
-  </si>
-  <si>
-    <t>377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Market-based PCE</t>
-  </si>
-  <si>
-    <t>DPCMRA</t>
-  </si>
-  <si>
-    <t>Durable goods:</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Market-based PCE motor vehicles and parts</t>
-  </si>
-  <si>
-    <t>DMOMRA</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Market-based PCE durable goods other than motor vehicles and parts</t>
-  </si>
-  <si>
-    <t>DDUMRA</t>
-  </si>
-  <si>
-    <t>Nondurable goods:</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Market-based PCE food and beverages purchased for off-premises consumption</t>
-  </si>
-  <si>
-    <t>DMFXRA</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Market-based PCE clothing and footwear</t>
-  </si>
-  <si>
-    <t>DCLMRA</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Market-based PCE gasoline and other energy goods</t>
-  </si>
-  <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Market-based PCE other nondurable goods</t>
-  </si>
-  <si>
-    <t>DNDXRA</t>
-  </si>
-  <si>
-    <t>Services:</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Market-based PCE services</t>
-  </si>
-  <si>
-    <t>DSEMRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Of which:</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Market-based PCE housing services</t>
-  </si>
-  <si>
-    <t>DHSMRA</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Market-based PCE household utilities</t>
-  </si>
-  <si>
-    <t>387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Market-based PCE health care</t>
-  </si>
-  <si>
-    <t>388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Market-based PCE transportation services</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Market-based PCE recreation services</t>
-  </si>
-  <si>
-    <t>DRCMRA</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Market-based PCE food services and accommodations</t>
-  </si>
-  <si>
-    <t>DFSMRA</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Market-based PCE financial services and insurance</t>
-  </si>
-  <si>
-    <t>DFIMRA</t>
-  </si>
-  <si>
-    <t>392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Market-based PCE other services</t>
-  </si>
-  <si>
-    <t>DOTMRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Of which:</t>
-  </si>
-  <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Market-based PCE communication services</t>
-  </si>
-  <si>
-    <t>394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Market-based PCE education</t>
-  </si>
-  <si>
-    <t>395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Market-based PCE professional services</t>
-  </si>
-  <si>
-    <t>DPRMRA</t>
-  </si>
-  <si>
-    <t>396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Market-based PCE personal care and clothing services</t>
-  </si>
-  <si>
-    <t>397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Market-based PCE child care</t>
-  </si>
-  <si>
-    <t>398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Market-based PCE household maintenance</t>
-  </si>
-  <si>
-    <t>DHMMRA</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>Market-based PCE food and energy</t>
-  </si>
-  <si>
-    <t>DPMFRA</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>Market-based PCE excluding food</t>
-  </si>
-  <si>
-    <t>DMXFRA</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>Market-based PCE excluding energy</t>
-  </si>
-  <si>
-    <t>DPMERA</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>Market-based PCE excluding food and energy</t>
-  </si>
-  <si>
-    <t>DPCXRA</t>
   </si>
 </sst>
 </file>
@@ -4017,7 +3699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6162A5-9014-405D-97EA-93197010368D}">
-  <dimension ref="A1:D410"/>
+  <dimension ref="A1:D369"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4044,9 +3726,6 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
@@ -8828,239 +8507,211 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="344" spans="1:4">
-      <c r="A344" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B344">
-        <v>2</v>
-      </c>
-      <c r="C344" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D344" t="s">
-        <v>1031</v>
-      </c>
-    </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B345">
         <v>3</v>
       </c>
       <c r="C345" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="D345" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B346">
         <v>4</v>
       </c>
       <c r="C346" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="D346" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="B347">
         <v>4</v>
       </c>
       <c r="C347" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="D347" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="B348">
         <v>4</v>
       </c>
       <c r="C348" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="D348" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B349">
         <v>3</v>
       </c>
       <c r="C349" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="D349" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B350">
         <v>3</v>
       </c>
       <c r="C350" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="D350" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B351">
         <v>3</v>
       </c>
       <c r="C351" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="D351" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B352">
         <v>3</v>
       </c>
       <c r="C352" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="D352" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="B353">
         <v>3</v>
       </c>
       <c r="C353" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D353" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="B354">
         <v>3</v>
       </c>
       <c r="C354" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D354" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="B355">
         <v>3</v>
       </c>
       <c r="C355" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="D355" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B356">
         <v>3</v>
       </c>
       <c r="C356" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D356" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4">
-      <c r="A357" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B357">
-        <v>2</v>
-      </c>
-      <c r="C357" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D357" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="B358">
         <v>3</v>
       </c>
       <c r="C358" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="D358" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="B359">
         <v>4</v>
       </c>
       <c r="C359" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="D359" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="B360">
         <v>4</v>
       </c>
       <c r="C360" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D360" t="s">
         <v>555</v>
@@ -9068,13 +8719,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="B361">
         <v>4</v>
       </c>
       <c r="C361" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="D361" t="s">
         <v>567</v>
@@ -9082,55 +8733,55 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="B362">
         <v>3</v>
       </c>
       <c r="C362" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="D362" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="B363">
         <v>3</v>
       </c>
       <c r="C363" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="D363" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="B364">
         <v>3</v>
       </c>
       <c r="C364" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="D364" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B365">
         <v>3</v>
       </c>
       <c r="C365" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="D365" t="s">
         <v>978</v>
@@ -9138,13 +8789,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="B366">
         <v>3</v>
       </c>
       <c r="C366" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="D366" t="s">
         <v>981</v>
@@ -9152,579 +8803,48 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="B367">
         <v>3</v>
       </c>
       <c r="C367" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="D367" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="B368">
         <v>3</v>
       </c>
       <c r="C368" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="D368" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="B369">
         <v>3</v>
       </c>
       <c r="C369" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="D369" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4">
-      <c r="B370">
-        <v>0</v>
-      </c>
-      <c r="C370" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4">
-      <c r="A371" t="s">
-        <v>1104</v>
-      </c>
-      <c r="B371">
-        <v>1</v>
-      </c>
-      <c r="C371" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D371" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4">
-      <c r="A372" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B372">
-        <v>1</v>
-      </c>
-      <c r="C372" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D372" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4">
-      <c r="A373" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B373">
-        <v>1</v>
-      </c>
-      <c r="C373" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D373" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4">
-      <c r="A374" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B374">
-        <v>1</v>
-      </c>
-      <c r="C374" t="s">
-        <v>1114</v>
-      </c>
-      <c r="D374" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4">
-      <c r="A375" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B375">
-        <v>1</v>
-      </c>
-      <c r="C375" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D375" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="376" spans="1:4">
-      <c r="A376" t="s">
-        <v>1119</v>
-      </c>
-      <c r="B376">
-        <v>1</v>
-      </c>
-      <c r="C376" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D376" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4">
-      <c r="A377" t="s">
-        <v>1122</v>
-      </c>
-      <c r="B377">
-        <v>1</v>
-      </c>
-      <c r="C377" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D377" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4">
-      <c r="A378" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B378">
-        <v>1</v>
-      </c>
-      <c r="C378" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D378" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="379" spans="1:4">
-      <c r="B379">
-        <v>0</v>
-      </c>
-      <c r="C379" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4">
-      <c r="A380" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B380">
-        <v>2</v>
-      </c>
-      <c r="C380" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D380" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="381" spans="1:4">
-      <c r="B381">
-        <v>0</v>
-      </c>
-      <c r="C381" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="382" spans="1:4">
-      <c r="A382" t="s">
-        <v>1133</v>
-      </c>
-      <c r="B382">
-        <v>1</v>
-      </c>
-      <c r="C382" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D382" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="383" spans="1:4">
-      <c r="A383" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B383">
-        <v>1</v>
-      </c>
-      <c r="C383" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D383" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="384" spans="1:4">
-      <c r="B384">
-        <v>0</v>
-      </c>
-      <c r="C384" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="385" spans="1:4">
-      <c r="A385" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B385">
-        <v>1</v>
-      </c>
-      <c r="C385" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D385" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4">
-      <c r="A386" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B386">
-        <v>1</v>
-      </c>
-      <c r="C386" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D386" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4">
-      <c r="A387" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B387">
-        <v>1</v>
-      </c>
-      <c r="C387" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D387" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="388" spans="1:4">
-      <c r="A388" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B388">
-        <v>1</v>
-      </c>
-      <c r="C388" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D388" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4">
-      <c r="B389">
-        <v>0</v>
-      </c>
-      <c r="C389" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4">
-      <c r="A390" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B390">
-        <v>1</v>
-      </c>
-      <c r="C390" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D390" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4">
-      <c r="B391">
-        <v>2</v>
-      </c>
-      <c r="C391" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4">
-      <c r="A392" t="s">
-        <v>1156</v>
-      </c>
-      <c r="B392">
-        <v>2</v>
-      </c>
-      <c r="C392" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D392" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="393" spans="1:4">
-      <c r="A393" t="s">
-        <v>1159</v>
-      </c>
-      <c r="B393">
-        <v>2</v>
-      </c>
-      <c r="C393" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D393" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="394" spans="1:4">
-      <c r="A394" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B394">
-        <v>2</v>
-      </c>
-      <c r="C394" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D394" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="395" spans="1:4">
-      <c r="A395" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B395">
-        <v>2</v>
-      </c>
-      <c r="C395" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D395" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="396" spans="1:4">
-      <c r="A396" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B396">
-        <v>2</v>
-      </c>
-      <c r="C396" t="s">
-        <v>1166</v>
-      </c>
-      <c r="D396" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="397" spans="1:4">
-      <c r="A397" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B397">
-        <v>2</v>
-      </c>
-      <c r="C397" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D397" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="398" spans="1:4">
-      <c r="A398" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B398">
-        <v>2</v>
-      </c>
-      <c r="C398" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D398" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4">
-      <c r="A399" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B399">
-        <v>2</v>
-      </c>
-      <c r="C399" t="s">
-        <v>1175</v>
-      </c>
-      <c r="D399" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="400" spans="1:4">
-      <c r="B400">
-        <v>3</v>
-      </c>
-      <c r="C400" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="401" spans="1:4">
-      <c r="A401" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B401">
-        <v>3</v>
-      </c>
-      <c r="C401" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D401" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4">
-      <c r="A402" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B402">
-        <v>3</v>
-      </c>
-      <c r="C402" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D402" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="403" spans="1:4">
-      <c r="A403" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B403">
-        <v>3</v>
-      </c>
-      <c r="C403" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D403" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="404" spans="1:4">
-      <c r="A404" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B404">
-        <v>3</v>
-      </c>
-      <c r="C404" t="s">
-        <v>1186</v>
-      </c>
-      <c r="D404" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4">
-      <c r="A405" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B405">
-        <v>3</v>
-      </c>
-      <c r="C405" t="s">
-        <v>1188</v>
-      </c>
-      <c r="D405" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4">
-      <c r="A406" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B406">
-        <v>3</v>
-      </c>
-      <c r="C406" t="s">
-        <v>1190</v>
-      </c>
-      <c r="D406" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4">
-      <c r="A407" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B407">
-        <v>0</v>
-      </c>
-      <c r="C407" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D407" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4">
-      <c r="A408" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B408">
-        <v>0</v>
-      </c>
-      <c r="C408" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D408" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4">
-      <c r="A409" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B409">
-        <v>0</v>
-      </c>
-      <c r="C409" t="s">
-        <v>1199</v>
-      </c>
-      <c r="D409" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="410" spans="1:4">
-      <c r="A410" t="s">
-        <v>1201</v>
-      </c>
-      <c r="B410">
-        <v>0</v>
-      </c>
-      <c r="C410" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D410" t="s">
-        <v>1203</v>
+        <v>1096</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D369" xr:uid="{1B6162A5-9014-405D-97EA-93197010368D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>